--- a/output/roomself_excel/8684.xlsx
+++ b/output/roomself_excel/8684.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>369488</v>
+        <v>79837</v>
       </c>
       <c r="D2" t="n">
-        <v>7356</v>
+        <v>2316</v>
       </c>
       <c r="E2" t="n">
-        <v>898</v>
+        <v>313</v>
       </c>
       <c r="F2" t="n">
-        <v>589</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>97664</v>
+        <v>198386</v>
       </c>
       <c r="D3" t="n">
-        <v>2568</v>
+        <v>4420</v>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>589</v>
       </c>
       <c r="F3" t="n">
-        <v>308</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115968</v>
+        <v>97664</v>
       </c>
       <c r="D4" t="n">
-        <v>2916</v>
+        <v>2568</v>
       </c>
       <c r="E4" t="n">
-        <v>491</v>
+        <v>366</v>
       </c>
       <c r="F4" t="n">
-        <v>270</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44973</v>
+        <v>115968</v>
       </c>
       <c r="D5" t="n">
-        <v>1736</v>
+        <v>2916</v>
       </c>
       <c r="E5" t="n">
-        <v>263</v>
+        <v>491</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55945</v>
+        <v>44973</v>
       </c>
       <c r="D6" t="n">
-        <v>2008</v>
+        <v>1736</v>
       </c>
       <c r="E6" t="n">
-        <v>351</v>
+        <v>263</v>
       </c>
       <c r="F6" t="n">
-        <v>183</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45937</v>
+        <v>55945</v>
       </c>
       <c r="D7" t="n">
-        <v>2156</v>
+        <v>2008</v>
       </c>
       <c r="E7" t="n">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="F7" t="n">
-        <v>101</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>53970</v>
+        <v>91265</v>
       </c>
       <c r="D9" t="n">
-        <v>1868</v>
+        <v>3340</v>
       </c>
       <c r="E9" t="n">
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="F9" t="n">
-        <v>226</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25650</v>
+        <v>53970</v>
       </c>
       <c r="D10" t="n">
-        <v>1284</v>
+        <v>1868</v>
       </c>
       <c r="E10" t="n">
-        <v>166</v>
+        <v>273</v>
       </c>
       <c r="F10" t="n">
-        <v>130</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -678,6 +678,50 @@
       </c>
       <c r="F11" t="n">
         <v>137</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>45937</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2156</v>
+      </c>
+      <c r="E12" t="n">
+        <v>138</v>
+      </c>
+      <c r="F12" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>25650</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1284</v>
+      </c>
+      <c r="E13" t="n">
+        <v>166</v>
+      </c>
+      <c r="F13" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/8684.xlsx
+++ b/output/roomself_excel/8684.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2316</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>313</v>
       </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>4420</v>
       </c>
-      <c r="E3" t="n">
-        <v>589</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>437</v>
+        <v>557</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>656</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2568</v>
       </c>
-      <c r="E4" t="n">
-        <v>366</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>308</v>
+        <v>276</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>334</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>2916</v>
       </c>
-      <c r="E5" t="n">
-        <v>491</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>270</v>
+        <v>238</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>459</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,20 @@
       <c r="D6" t="n">
         <v>1736</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>263</v>
       </c>
-      <c r="F6" t="n">
-        <v>16</v>
-      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +669,27 @@
       <c r="D7" t="n">
         <v>2008</v>
       </c>
-      <c r="E7" t="n">
-        <v>351</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>183</v>
+        <v>335</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>167</v>
+      </c>
+      <c r="J7" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>1160</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>168</v>
       </c>
-      <c r="F8" t="n">
-        <v>16</v>
-      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +737,27 @@
       <c r="D9" t="n">
         <v>3340</v>
       </c>
-      <c r="E9" t="n">
-        <v>334</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>322</v>
+        <v>118</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>306</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +775,27 @@
       <c r="D10" t="n">
         <v>1868</v>
       </c>
-      <c r="E10" t="n">
-        <v>273</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>226</v>
+        <v>210</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>257</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +813,27 @@
       <c r="D11" t="n">
         <v>1044</v>
       </c>
-      <c r="E11" t="n">
-        <v>156</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>137</v>
+        <v>312</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>105</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -695,11 +851,27 @@
       <c r="D12" t="n">
         <v>2156</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>138</v>
       </c>
-      <c r="F12" t="n">
-        <v>85</v>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>106</v>
+      </c>
+      <c r="J12" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -717,11 +889,27 @@
       <c r="D13" t="n">
         <v>1284</v>
       </c>
-      <c r="E13" t="n">
-        <v>166</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>130</v>
+        <v>150</v>
+      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>114</v>
+      </c>
+      <c r="J13" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
